--- a/miltenyi-pms-dev/docs/meetings/2026-05-25-notifications-decision-matrix.xlsx
+++ b/miltenyi-pms-dev/docs/meetings/2026-05-25-notifications-decision-matrix.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Should goal-related notifications fire on in-app, email, or both?</t>
+          <t>Should goal-related notifications appear in the app bell, by email, or both?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Today: in-app fires on every event; email opt-in per-event (only mentor-assignment notifications fire email). The bell shows the in-app list; emails go via the SMTP relay when configured.</t>
+          <t>Today the bell always shows a new alert when something happens with a goal. Emails only go out for a few specific events (like mentor assignment changes and the welcome email). Goal events themselves are bell-only.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>In-app for all events. Email only on workflow-blocking events (goal submitted for approval, changes requested) so mentors and employees aren't waiting for someone who hasn't opened the app.</t>
+          <t>Keep the bell for every event. Add email only for the events that block someone's work — when an employee submits a goal that needs the mentor's approval, or when the mentor sends it back for changes.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -504,17 +504,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Do users need an opt-out / unsubscribe from goal emails?</t>
+          <t>Should users be able to turn off goal-related emails?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Today: no unsubscribe UI. SMTP simply doesn't fire if not configured org-wide. A user cannot mute individual categories.</t>
+          <t>There is no off-switch today. If the company has email turned on at the system level, every goal email goes to everyone who is supposed to receive one.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Add a per-user 'email me about my goals' toggle in Profile. In-app stays on always (it's a read-only feed, no spam pressure).</t>
+          <t>Add an 'email me about my goals' toggle in each user's Profile page. Bell notifications stay on for everyone — they're a quiet feed inside the app, not spam.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -527,17 +527,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Should HR see a goal-events digest separately from individual alerts?</t>
+          <t>Should HR get a separate summary of goal activity, or only be alerted on big events?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Today: HR doesn't get individual goal alerts (Mentor handles the approval). The HR dashboard's stalled-goals widget is the only HR-side surface tracking goal lifecycle.</t>
+          <t>Today HR doesn't get any per-event alert about goals. They see a 'stalled goals' card on the dashboard that flags goals waiting too long for the mentor's approval.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Keep HR out of per-event alerts. Optional: weekly summary showing approval velocity + stalled count (future scope).</t>
+          <t>Keep HR out of per-event alerts (avoids noise). Optional: a weekly summary email showing approval velocity and the stalled count, if HR finds that useful.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -550,17 +550,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Event: Employee submits goal for mentor approval</t>
+          <t>When an employee submits a goal for approval, who should be told and how?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: assigned mentor  /  Message: '{Employee name} submitted a goal for your approval.'</t>
+          <t>The mentor sees a bell notification: 'Bob Builder submitted a goal for your approval.' No email is sent.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Add email (workflow-blocking — mentor needs to act).</t>
+          <t>Keep the bell. Add email — this blocks the workflow until the mentor acts on it.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -573,17 +573,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor approves a single goal</t>
+          <t>When a mentor approves a single goal, how should the employee be told?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: goal owner  /  Message: 'Your goal was approved.'</t>
+          <t>The employee sees a bell notification: 'Your goal was approved.' No email.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Email optional (good news, can wait for app visit).</t>
+          <t>Keep the bell. Email is optional — this is good news that can wait for the employee to open the app.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -596,17 +596,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor requests changes on a goal</t>
+          <t>When a mentor sends a goal back for revisions, how should the employee be told?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: goal owner  /  Message: includes mentor's feedback inline.</t>
+          <t>The employee sees a bell notification that includes the mentor's feedback. No email.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email (workflow-blocking — employee needs to revise and resubmit).</t>
+          <t>Keep the bell. Add email — the employee needs to revise and resubmit, so this blocks their next step.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -619,17 +619,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor bulk-approves goals</t>
+          <t>When a mentor approves several goals at once (bulk approve), should each owner get a separate notification per goal?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓ (one per goal)  /  Email: ✗  /  Recipient: each goal owner  /  Message: 'Your goal was approved.'</t>
+          <t>Today every goal owner gets a separate bell alert for each of their goals that was approved — so one employee can see multiple alerts in a row.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Bulk-approve fires N notifications; consider collapsing into one summary per recipient ('3 of your goals were approved').</t>
+          <t>Roll up multiple approvals from the same mentor into a single summary: '3 of your goals were approved' instead of 3 separate alerts.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -642,17 +642,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor notifies employee inline (free-text via Notify button on goal detail)</t>
+          <t>When a mentor uses the 'Notify' button on a goal to send a free-text message, how should it be delivered?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: goal owner  /  Message: mentor-typed text.</t>
+          <t>The employee sees a bell notification with whatever the mentor typed. No email.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Add email opt-in so the mentor can choose to send the typed note as an email too.</t>
+          <t>Keep the bell. Add an option for the mentor to also send the message as an email when they want to.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
@@ -665,17 +665,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Event: Employee submits H1 / H2 self-review on a goal</t>
+          <t>When an employee submits their H1 or H2 self-review on a goal, who should be told?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: assigned mentor  /  Message: '{Employee name} submitted a {H1|H2} self-review.'</t>
+          <t>The mentor sees a bell notification: 'Bob Builder submitted an H1 self-review.' No email.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Email optional — the mentor's review queue surfaces this when they next open the app.</t>
+          <t>Keep the bell. Email is optional — the mentor's review queue shows this when they next open the app.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -688,17 +688,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor submits their H1 / H2 review on an employee's goal</t>
+          <t>When a mentor submits their H1 or H2 review on an employee's goal, how should the employee be told?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: goal owner  /  Message: 'Your mentor submitted their {H1|H2} review.'</t>
+          <t>The employee sees a bell notification: 'Your mentor submitted their H1 review.' No email.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. No email — the H1/H2 review is read-only feedback, not workflow-blocking for the employee.</t>
+          <t>Keep the bell. No email needed — this is read-only feedback for the employee, not something they need to act on right away.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
@@ -711,17 +711,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>POTENTIAL: Stalled-goal nudge (auto-remind mentor when a goal has been PENDING_APPROVAL for &gt;N days)</t>
+          <t>POTENTIAL: Should the system automatically remind mentors about goals that have been waiting for their approval too long?</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Today: HR sees a stalled-goals chase list on the dashboard but the mentor receives no auto-reminder.</t>
+          <t>Today HR sees a 'stalled goals' chase list on the dashboard. Mentors get no automatic reminder; they have to open the app and look.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Add a daily cron at 9am org-tz that pushes one in-app + email to mentors with goals stalled ≥7 days. Configurable threshold.</t>
+          <t>Add an automatic daily reminder (bell + email) to mentors with any goals waiting 7+ days for their approval. The day threshold should be configurable.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -782,17 +782,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Should annual-review events fire to multiple recipients (mentor + HR_MyOrg) or just the direct owner?</t>
+          <t>When something happens with an annual review, should multiple people be notified (e.g. mentor + HR), or just the one person directly involved?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Today: each event has exactly one recipient (the mentor on submission, the employee on completion). HR_MyOrg sees the calibration grid but receives no per-event alert.</t>
+          <t>Today each event has exactly one recipient. The mentor is told when the employee submits their self-appraisal; the employee is told when the mentor finishes their evaluation. HR is not alerted per event — they see the calibration grid in the app.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Keep single-recipient default. Optional 'HR copy' org setting for events that transition status (self-submitted, mentor-eval done, management rating published).</t>
+          <t>Keep the single-recipient default. Add an optional company-wide setting that gives HR a copy whenever a review changes state (self-appraisal submitted, mentor evaluation done, final rating published).</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -805,17 +805,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Should the employee be notified when HR sets / overwrites the Management rating?</t>
+          <t>Should the employee be told when HR publishes or updates their final 'management' rating?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Today: yes — in-app fires with 'Your final rating is now available' (first publish) or 'Your final rating was updated' (recalibration). A same-value re-save stays silent.</t>
+          <t>Yes — today the employee sees a bell notification: 'Your final rating is now available' on first publish, or 'Your final rating was updated' if HR changes it later. If HR re-saves the same value, no notification fires.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Keep this. The per-row final_rating_enabled gate + the org-wide annual_review_final_rating_visible flag still control whether the employee can actually see the number.</t>
+          <t>Keep this. Whether the employee can actually see the rating number itself is governed by separate visibility settings — that's not changed by this notification policy.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -828,17 +828,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Should HR be notified when every mentor has finished evaluations for a cycle (so they can begin calibration)?</t>
+          <t>Should HR be told when every mentor in the company has finished their evaluations, so they know calibration can begin?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Today: no — HR has to check the calibration grid manually.</t>
+          <t>Today HR has to check the calibration grid manually to see if everyone has filed.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Add a daily check: when 100% of active employees' reviews are in PENDING_MANAGEMENT state for the active FY, fire a one-time in-app + email to HR_MyOrg 'Calibration ready: all mentor evaluations are in.'</t>
+          <t>Add a one-time bell + email to HR when all employee reviews have reached the 'pending management' stage: 'Calibration ready — every mentor has filed their evaluation.'</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -851,17 +851,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Event: Employee submits annual self-appraisal</t>
+          <t>When an employee submits their annual self-appraisal, who should be told and how?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: assigned mentor  /  Message: '{Employee name} submitted their {FY26-27} self-appraisal.'</t>
+          <t>The mentor sees a bell notification: 'Bob Builder submitted their FY26-27 self-appraisal.' No email.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email (year-end workflow — mentors need to be reminded to start their evaluations).</t>
+          <t>Keep the bell. Add email — the annual review is a once-a-year event; mentors should be nudged out of the app to start their own evaluation.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -874,17 +874,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Event: Mentor submits annual evaluation</t>
+          <t>When a mentor submits their annual evaluation of an employee, how should the employee be told?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: employee  /  Message: 'Your mentor submitted their evaluation for {FY26-27}.'</t>
+          <t>The employee sees a bell notification: 'Your mentor submitted their evaluation for FY26-27.' No email.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email (year-end milestone for the employee).</t>
+          <t>Keep the bell. Add email — it's a year-end milestone the employee should know about.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -897,17 +897,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Event: HR_MyOrg publishes / updates the Management rating</t>
+          <t>When HR publishes or updates an employee's final rating, how should the employee be told?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: employee  /  Message: 'Your final rating is now available' OR 'Your final rating was updated.'</t>
+          <t>The employee sees a bell notification only. No email.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email. This is the final compensation-adjacent event for the year and warrants a notification outside the app.</t>
+          <t>Keep the bell. Add email — this is the year-end compensation-adjacent event; it warrants a notification outside the app.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -968,17 +968,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Should PMs be auto-reminded as the cycle close approaches?</t>
+          <t>Should PMs be automatically reminded as the review cycle close approaches?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Today: no reminders. The PM sees their queue in the app and must remember to file. HR sees a project-review completion card on the dashboard funnel.</t>
+          <t>No reminders today. The PM sees their pending-reviews queue in the app and has to remember to file. HR sees a completion card on the dashboard but doesn't actively nudge PMs.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Add a cron-based reminder N days before cycle close (default 7) to PMs with any PENDING reviews on their team. In-app + email.</t>
+          <t>Add an automatic reminder (bell + email) sent 7 days before the cycle closes, to any PM with reviews still pending.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -991,17 +991,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>When the project assignment ends mid-cycle, should we notify the PM that the review window is shortened?</t>
+          <t>When an employee rolls off a project mid-cycle, should the PM be told their review window for that employee has shortened?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Today: no auto-message. The assignment end-date silently shortens the PM's window on that team-member.</t>
+          <t>No automatic message today. The assignment end-date silently shortens the PM's window without any heads-up.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Add an in-app alert to the PM: '{Employee} rolled off {Project}; complete their {cycle} review by FY end or skip.' Email optional.</t>
+          <t>Add a bell alert to the PM: 'Bob rolled off ProjectX; complete his Q2 review by year-end or skip it.' Email is optional.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Should the secondary evaluator be alerted independently when the PM submits their primary review?</t>
+          <t>Should the secondary evaluator be told when the PM submits their primary review, prompting them to add their impact statement?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Today: yes — the secondary gets an in-app ping when the PM submits, prompting them to add the impact statement.</t>
+          <t>Yes — today the secondary gets a bell notification when the PM submits. No email.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Add email opt-in for secondaries who don't open the app daily.</t>
+          <t>Keep the bell. Add an email option for secondaries who don't open the app daily.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Event: PM submits a project review</t>
+          <t>When a PM submits a project review for one of their team members, how should the employee be told?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: the employee being reviewed  /  Message: 'Your PM submitted a project review for {project name}.'</t>
+          <t>The employee sees a bell notification: 'Your PM submitted a project review for ProjectX.' No email.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email (review visibility is important for the reviewee — keep them informed).</t>
+          <t>Keep the bell. Add email — the employee should know that feedback has been filed about their work on the project.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Event: Secondary evaluator adds impact statement</t>
+          <t>When a secondary evaluator adds their impact statement, how should the employee be told?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: the employee being reviewed  /  Message: 'A secondary evaluator added impact on your {project name} review.'</t>
+          <t>The employee sees a bell notification: 'A secondary evaluator added impact on your ProjectX review.' No email.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Email optional.</t>
+          <t>Keep the bell. Email is optional.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Event: PM EDITS a previously-submitted project review (status transitions back to draft → reviewed)</t>
+          <t>When a PM goes back and edits a project review they already submitted, how should the employee be told?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: the employee being reviewed  /  Message: 'Your PM updated their project review for {project name}.'</t>
+          <t>The employee sees a bell notification: 'Your PM updated their project review for ProjectX.' No email.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Email only if material rating change (1+ step on the 1–5 scale). Avoids edit-thrash spam.</t>
+          <t>Keep the bell. Send an email only if the rating actually changed by a step or more on the 1–5 scale — otherwise minor edits would spam the employee's inbox.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Event: Project assigned with a secondary evaluator</t>
+          <t>When a project is created with a secondary evaluator, how should that person be told?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: secondary  /  Message: assignment + project name.</t>
+          <t>The secondary sees a bell notification with the project name. No email.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email (the secondary needs to know they're on a new project; they likely don't poll the app for this).</t>
+          <t>Keep the bell. Add email — the secondary needs to know they're on a new project; they likely don't poll the app to find out.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -1129,17 +1129,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Event: Project's secondary evaluator changed</t>
+          <t>When a project's secondary evaluator is reassigned, who should be told and how?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Today: notify both old ("you have been removed") and new ("you have been assigned") secondaries. In-app only.</t>
+          <t>The old secondary gets a bell notification ('You have been removed'), and the new secondary gets one ('You have been assigned'). Bell only — no email.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app + add email to the NEW secondary (so they know they're now on the hook).</t>
+          <t>Keep the bell for both. Add email to the NEW secondary so they know they're on the hook.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Event: Project marked complete</t>
+          <t>When a project is marked complete, who should be told?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipients: PM + all assigned employees + secondary (via notify_many).  /  Message: 'Project {name} has been marked complete.'</t>
+          <t>Bell notification to: the PM, every assigned employee, the secondary. No email.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app for everyone. Email opt-in.</t>
+          <t>Keep the bell for everyone. Email is opt-in.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Event: Project member assignment ended (rolled off mid-project)</t>
+          <t>When someone is rolled off a project mid-stream, who should be told?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✗  /  Recipient: the rolled-off employee + their PM  /  Message: assignment ended date.</t>
+          <t>Bell notification to the person who rolled off and to their PM, showing the end date. No email.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Keep in-app. Email optional.</t>
+          <t>Keep the bell. Email is optional.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>When HR_Miltenyi creates a user, should HR_MyOrg be informed (audit trail)?</t>
+          <t>When HR Miltenyi creates a new user account, should HR MyOrg be told about it for audit purposes?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Today: no. The audit is in the User row's created_at + the creating user's ID isn't recorded as a column.</t>
+          <t>No today. The new user account is recorded with its creation timestamp, but HR MyOrg is not actively notified.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Optional in-app digest to HR_MyOrg: 'N users created today by {HR_Miltenyi name}.' Daily cron. Not per-event.</t>
+          <t>Optional daily summary email to HR MyOrg: 'N new users were created today by [HR Miltenyi name].' Not per-event.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -1269,17 +1269,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Should a deactivated user receive any notification (the JWT is already blocked)?</t>
+          <t>Should a deactivated user receive any notification (knowing they can't log in anyway)?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Today: no — the notify() service short-circuits writes to deactivated recipients (PR #60). The deactivated user cannot log in to see anything anyway.</t>
+          <t>No. The system blocks any new notifications from being sent to a deactivated account, since the user can't log in to read them.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Keep current behavior. If HR reactivates the user, fire a 'welcome back' in-app + email (already implemented).</t>
+          <t>Keep this. If HR later reactivates the user, a 'welcome back' notification fires automatically (already implemented).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -1292,17 +1292,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Should the user's manager / mentor be notified when their direct report's profile changes (function / designation / etc.)?</t>
+          <t>Should an employee's mentor be told when the employee's profile changes (function, designation, etc.)?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Today: no. Only mentor-assignment changes fire a notification.</t>
+          <t>No. Only mentor-assignment changes themselves fire a notification — the rest of the profile is silent.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Skip for now — too chatty if a function/designation change fires N notifications per mentee under the same mentor.</t>
+          <t>Skip for now. Mentors with many mentees would get a flood of alerts every time HR updates a function or designation.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Event: New user account created by HR</t>
+          <t>When HR creates a new user account, how should the new user be told?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✓  (welcome email with temp password)  /  Recipient: the new user  /  In-app message: 'Welcome to PMS — your account is ready.'</t>
+          <t>The new user gets a welcome email with their temporary password, plus a bell notification on first login: 'Welcome to PMS — your account is ready.'</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Event: User's mentor assigned / reassigned / unassigned</t>
+          <t>When an employee's mentor is assigned, changed, or removed, who should be told?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✓  /  Recipients: the mentee + the new mentor (if any)  /  Message: includes new mentor name or unassignment notice.</t>
+          <t>Both the employee and the new mentor (if any) get a bell notification and an email describing the change.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Keep both. Mentor relationship is foundational — user needs to know who reviews their work.</t>
+          <t>Keep both. The mentor relationship is foundational — the employee needs to know who reviews their work.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Event: User account reactivated</t>
+          <t>When HR reactivates a previously deactivated user, how should the user be told?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>In-app: ✓  /  Email: ✓  /  Recipient: the reactivated user  /  Message: 'Your account has been reactivated. You can sign in again.'</t>
+          <t>Bell notification + email: 'Your account has been reactivated. You can sign in again.'</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Event: Password reset requested</t>
+          <t>When a user requests a password reset, how is the reset link delivered?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Email: ✓ (reset link, 15-min expiry)  /  In-app: ✗ (user is logged out)  /  Recipient: requesting user.</t>
+          <t>Email only (the reset link is valid for 15 minutes). No bell notification — the user is locked out of the app at that moment.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Keep email-only. The user is locked out of the app when this fires; in-app is unreachable.</t>
+          <t>Keep email-only. The user can't see the bell when they're locked out.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Event: Password changed (self-service)</t>
+          <t>When a user successfully changes their own password, should they get a confirmation?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Today: no notification on success. The user clicks Change Password and the modal closes.</t>
+          <t>Today there's no notification on success. The Change Password modal just closes.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Add a confirmation email (security: alerts the user if the change wasn't them). In-app banner on next login.</t>
+          <t>Add a confirmation email — protects the user if someone else made the change. Optionally also a short on-screen banner on next login.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Event: must_change_password flag set by HR (forced reset)</t>
+          <t>When HR forces a user to change their password on next login, should the user be told in advance?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Today: in-app banner gates the app on next login. No email.</t>
+          <t>On their next login the user sees an on-screen banner that gates the app until they pick a new password. No email is sent beforehand.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Add an email so the user knows to expect the gate on next login: 'Your password was reset by HR. You'll be asked to choose a new one when you sign in.'</t>
+          <t>Add an email when HR triggers this: 'Your password was reset by HR. You'll be asked to choose a new one when you sign in.'</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -1501,21 +1501,21 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Channel split: which categories of notification go to which channel by default?</t>
+          <t>By default, which kinds of events should go where — bell, email, or both?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Today: every notify() call writes in-app. Email is opt-in per call (currently only mentor-assignment + welcome + password-reset + reactivation fire email).</t>
+          <t>Today every event writes to the bell. Emails are opt-in per event — currently only mentor-assignment changes, the welcome email, password reset, and reactivation send email.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Default matrix:
-  • Workflow-blocking (approval requested, changes requested) → in-app + email
-  • Status updates (your review submitted) → in-app + email opt-in
-  • Read-only feedback (your H1 review is in) → in-app only
-  • Security events (password reset, login from new device) → email mandatory</t>
+          <t>Default policy:
+  • Workflow-blocking events (approval requested, changes requested) → bell + email
+  • Status updates (your review was submitted) → bell + email opt-in
+  • Read-only feedback (your H1 review is in) → bell only
+  • Security events (password reset, login from a new device) → email always</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -1528,17 +1528,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Email digest cadence: should low-priority notifications be batched into a daily / weekly digest?</t>
+          <t>Should low-priority emails be batched into a daily or weekly digest?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Today: every email is fire-and-forget at event time. No digest.</t>
+          <t>Every email fires the moment its event happens. There's no digest today.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Add an opt-in 'send me a daily digest at 9am' switch in Profile for non-blocking categories. Workflow-blocking emails fire immediately regardless.</t>
+          <t>Add an opt-in 'send me a daily digest at 9am' switch in Profile, covering non-blocking events. Workflow-blocking emails still fire immediately, regardless of digest setting.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Per-user notification preferences: where do they live?</t>
+          <t>Where do users manage their own notification preferences?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Today: no per-user preferences. Notifications fire to everyone.</t>
+          <t>Today there's no preferences screen. Everyone gets the same notifications.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Add a Profile → Notifications tab with toggles per category (Goals / Annual Reviews / Project Reviews / Admin) and per channel (in-app on/off, email on/off, digest frequency).</t>
+          <t>Add a Profile → Notifications page with on/off toggles per category (Goals / Annual Reviews / Project Reviews / Admin) and per channel (bell on/off, email on/off, digest frequency).</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -1574,17 +1574,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Should HR be able to bcc themselves on every notification (observation mode)?</t>
+          <t>Should HR be able to BCC themselves on every notification (observation / audit mode)?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Today: no. HR's only audit surface is the Notification table directly (no UI).</t>
+          <t>No. HR has no way to see what notifications have been sent across the company.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Skip. Future: a 'Notification audit log' admin page that lists every fired notification across the org with filters.</t>
+          <t>Skip for now. Future: a Notification Audit Log page in Admin that lists every notification sent across the company, with filters by category, recipient, and date.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Unsubscribe links in emails — required for compliance / nicety?</t>
+          <t>Should emails include an unsubscribe link in the footer?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Today: emails don't include unsubscribe footers.</t>
+          <t>Today's emails don't have any unsubscribe footer.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Add a one-click 'manage email preferences' link footer that deep-links to Profile → Notifications. Not a hard unsubscribe — keeps security emails mandatory.</t>
+          <t>Add a 'manage email preferences' link in the footer that takes the user to Profile → Notifications. Not a hard unsubscribe — security emails (like password reset) always go out.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -1620,17 +1620,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Quiet hours: should emails respect a per-user quiet window (e.g. don't email between 8pm and 7am org-tz)?</t>
+          <t>Should emails respect a per-user quiet window (e.g. don't email between 8pm and 7am local time)?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Today: emails fire immediately regardless of time.</t>
+          <t>Today emails fire immediately, regardless of time of day.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Add quiet hours to the per-user preferences in Profile. In-app notifications still fire (user reads on their schedule). Security emails ignore quiet hours.</t>
+          <t>Add quiet hours to the per-user preferences page. Bell notifications still fire (the user reads them when they want). Security emails ignore quiet hours.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>POTENTIAL: Slack / MS Teams integration</t>
+          <t>POTENTIAL: Should the system integrate with Slack or Microsoft Teams?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Today: not implemented.</t>
+          <t>Not implemented today.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Future scope. Bind a Slack webhook to the user's profile; notify() learns a 'slack' channel alongside in-app/email. Most value for mentor approval queues + HR reminders.</t>
+          <t>Future scope. Highest value for mentor approval queues and HR reminders — those are the people most likely to live in Slack/Teams during the workday.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>POTENTIAL: Mobile push (PWA / native app)</t>
+          <t>POTENTIAL: Should the system support mobile push notifications (mobile app or browser push)?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Today: not implemented. The app is web-only.</t>
+          <t>Not implemented today. The app is web-only.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Future scope. Lower priority — emails cover most cases until a mobile presence is justified by usage.</t>
+          <t>Future scope. Lower priority — email covers most cases until there's a mobile presence to justify the build.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
@@ -1689,17 +1689,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>POTENTIAL: SMS for security-critical events (password reset, account locked)</t>
+          <t>POTENTIAL: Should the system send SMS for security-critical events (password reset, account locked)?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Today: not implemented. Email is the only out-of-app channel.</t>
+          <t>Not implemented today. Email is the only out-of-app channel.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Future scope. Tradeoff: SMS cost + carrier reliability vs. email's reach. Email + TOTP / passkeys may be enough.</t>
+          <t>Future scope. Trade-off: SMS cost and carrier reliability vs. email's reach. Email plus two-factor / passkeys may be enough.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -1712,17 +1712,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>How long are in-app notifications retained in the bell?</t>
+          <t>How long should bell notifications be kept?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Today: every notification persists forever in the Notification table. The bell shows the most recent 20 (notification_routes.get_topbar_summary limit=20).</t>
+          <t>Every notification is kept forever in the database. The bell shows the most recent 20.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Auto-archive read notifications older than 90 days (soft-delete on the table, kept for audit). Unread notifications never auto-archive.</t>
+          <t>Auto-archive read notifications older than 90 days — they're still kept for audit, just not shown in the bell anymore. Unread notifications never auto-archive.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
@@ -1735,17 +1735,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>When a sender is deactivated, do their historical notifications stay visible to recipients?</t>
+          <t>If someone is deactivated, should their past notifications stay visible in other users' bells?</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Today: yes. The notify() writer short-circuits NEW writes to deactivated recipients, but existing rows from a now-deactivated sender remain in recipients' bells. Documented as intentional in notification_routes.get_topbar_summary.</t>
+          <t>Yes. New notifications can no longer be sent to deactivated users, but old notifications written BY a now-deactivated person stay in the recipients' bells.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Keep current behavior. The notification represents a real past event; erasing it would erase audit history.</t>
+          <t>Keep this. The notification records a real past event — erasing it would erase history.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Notification audit / observability: where does HR see what fired?</t>
+          <t>Where should HR go to see what notifications have been sent across the company?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Today: HR has no UI to inspect the Notification table. They can only see what each user sees by logging in as them (not possible).</t>
+          <t>Today HR has no way to see this. They can only see what each user sees by logging in as them — which they can't do.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Add an HR-only Notifications Audit page (Admin Panel) that filters notifications by module / recipient / date range. Read-only — no editing.</t>
+          <t>Add an HR-only Notifications Audit page (in Admin Panel) that filters notifications by category, recipient, and date range. Read-only — no editing.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
